--- a/12629354.xlsx
+++ b/12629354.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python-MCA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D44761-03C7-4BF5-BCDD-EAA56EFC60A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D015AB-9FE7-4883-840E-3E4D52DF7425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,15 @@
   </si>
   <si>
     <t>tiring day</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>meduim</t>
+  </si>
+  <si>
+    <t>medium</t>
   </si>
 </sst>
 </file>
@@ -1846,7 +1855,9 @@
       <c r="A23" s="13">
         <v>46264</v>
       </c>
-      <c r="B23" s="14"/>
+      <c r="B23" s="14">
+        <v>360</v>
+      </c>
       <c r="C23" s="14">
         <v>10</v>
       </c>
@@ -1867,14 +1878,14 @@
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>190</v>
+        <v>550</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>1250</v>
+        <v>890</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="L23" s="16" t="s">
         <v>50</v>
@@ -1885,153 +1896,301 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B24" s="14">
+        <v>360</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>20</v>
+      </c>
+      <c r="E24" s="14">
+        <v>20</v>
+      </c>
+      <c r="F24" s="14">
+        <v>350</v>
+      </c>
+      <c r="G24" s="14">
+        <v>7</v>
+      </c>
+      <c r="H24" s="14">
+        <v>30</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>83</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>40</v>
+      </c>
+      <c r="D25" s="14">
+        <v>30</v>
+      </c>
+      <c r="E25" s="14">
+        <v>10</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>30</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>670</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>84</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>30</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>40</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>85</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>40</v>
+      </c>
+      <c r="E27" s="14">
+        <v>20</v>
+      </c>
+      <c r="F27" s="14">
+        <v>100</v>
+      </c>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="14">
+        <v>20</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>560</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>880</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B28" s="14">
+        <v>360</v>
+      </c>
+      <c r="C28" s="14">
+        <v>40</v>
+      </c>
+      <c r="D28" s="14">
+        <v>50</v>
+      </c>
+      <c r="E28" s="14">
+        <v>10</v>
+      </c>
+      <c r="F28" s="14">
+        <v>150</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>30</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+        <v>800</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>100</v>
+      </c>
+      <c r="E29" s="14">
+        <v>20</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>40</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>550</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>890</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B30" s="14">
+        <v>360</v>
+      </c>
+      <c r="C30" s="14">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>40</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>840</v>
       </c>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
@@ -2039,21 +2198,31 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
+      <c r="A31" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B31" s="14">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>180</v>
+      </c>
+      <c r="E31" s="14">
+        <v>40</v>
+      </c>
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>610</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>830</v>
       </c>
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
@@ -2061,21 +2230,27 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
+      <c r="A32" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B32" s="14">
+        <v>360</v>
+      </c>
+      <c r="C32" s="14">
+        <v>20</v>
+      </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>380</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1060</v>
       </c>
       <c r="K32" s="16"/>
       <c r="L32" s="16"/>
